--- a/Caso-Integrado/Caso-Integrado-modelo.xlsx
+++ b/Caso-Integrado/Caso-Integrado-modelo.xlsx
@@ -20,7 +20,7 @@
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Calendário!$B$1:$Z$55</definedName>
     <definedName function="false" hidden="false" localSheetId="5" name="_xlnm.Print_Area" vbProcedure="false">Checklist!$B$1:$E$24</definedName>
-    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Estudos!$B$1:$G$33</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">Estudos!$B$1:$G$38</definedName>
     <definedName function="false" hidden="false" localSheetId="6" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 1 - Pizzaria'!$B$1:$Z$48</definedName>
     <definedName function="false" hidden="false" localSheetId="7" name="_xlnm.Print_Area" vbProcedure="false">'Exemplo 2 - Indústria'!$B$1:$Z$46</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">Instruções!$B$1:$C$43</definedName>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="404">
   <si>
     <t xml:space="preserve">Caso integrado — Como usar esta planilha</t>
   </si>
@@ -254,7 +254,7 @@
     <t xml:space="preserve">Estudos</t>
   </si>
   <si>
-    <t xml:space="preserve">Os 29 estudos da série, com o grupo e o ritmo recomendado. Alimenta as listas suspensas.</t>
+    <t xml:space="preserve">Os 34 estudos da série, com o grupo e o ritmo recomendado. Alimenta as listas suspensas.</t>
   </si>
   <si>
     <t xml:space="preserve">Painel</t>
@@ -509,6 +509,18 @@
     <t xml:space="preserve">Diagnóstico requisito a requisito, uma vez por ano.</t>
   </si>
   <si>
+    <t xml:space="preserve">ISO 9001:2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISO 9001:2026: o que muda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quando necessário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uma vez, na transição, com o plano lido no calendário.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Escopo e liderança</t>
   </si>
   <si>
@@ -602,9 +614,6 @@
     <t xml:space="preserve">Projeto e desenvolvimento</t>
   </si>
   <si>
-    <t xml:space="preserve">Quando necessário</t>
-  </si>
-  <si>
     <t xml:space="preserve">A cada produto ou serviço novo.</t>
   </si>
   <si>
@@ -668,6 +677,12 @@
     <t xml:space="preserve">A cada problema escolhido.</t>
   </si>
   <si>
+    <t xml:space="preserve">Histograma e CEP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cada subgrupo medido, com leitura mensal dos sinais.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ishikawa</t>
   </si>
   <si>
@@ -704,6 +719,12 @@
     <t xml:space="preserve">Programa com auditorias a cada semestre.</t>
   </si>
   <si>
+    <t xml:space="preserve">Técnica de auditoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cada auditoria interna, com a avaliação dos auditores.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Não conformidade</t>
   </si>
   <si>
@@ -734,6 +755,18 @@
     <t xml:space="preserve">Reclamações todo dia, pesquisa a cada trimestre.</t>
   </si>
   <si>
+    <t xml:space="preserve">Processo de certificação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auditoria do organismo a cada ano, com a preparação.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caso integrado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leitura mensal do calendário e dos fios abertos.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Painel do sistema integrado</t>
   </si>
   <si>
@@ -893,9 +926,6 @@
     <t xml:space="preserve">Percentual atendido</t>
   </si>
   <si>
-    <t xml:space="preserve">Caso integrado</t>
-  </si>
-  <si>
     <t xml:space="preserve">Exemplo preenchido, para consulta. Use as abas Rastro e Calendário para a sua organização.</t>
   </si>
   <si>
@@ -944,16 +974,16 @@
     <t xml:space="preserve">Os dois motivos principais</t>
   </si>
   <si>
-    <t xml:space="preserve">Causas confirmadas: escala igual todos os dias, pedidos sem agrupamento por bairro, endereço sem complemento.</t>
+    <t xml:space="preserve">Cinco causas confirmadas; quatro vão para o plano: escala igual todos os dias, pedidos sem agrupamento por bairro, endereço sem complemento e tempo medido só pela média do dia. A fila do forno fica para depois.</t>
   </si>
   <si>
     <t xml:space="preserve">Diagrama de 17/07/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">Três causas confirmadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Três ações: reforçar a escala no pico, agrupar os pedidos por bairro, tornar o complemento obrigatório.</t>
+    <t xml:space="preserve">Quatro causas para o plano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seis ações, de A1 a A6: reforçar a escala no pico, tornar o complemento obrigatório, treinar a expedição, agrupar os pedidos por bairro, medir o tempo por faixa de horário e atualizar a instrução da expedição.</t>
   </si>
   <si>
     <t xml:space="preserve">Plano de ação de 24/07/2026</t>
@@ -1154,13 +1184,13 @@
     <t xml:space="preserve">Causa: variação de espessura na extrusora 3, sem medidor em linha. Inspeção de 100% das bobinas do cliente A.</t>
   </si>
   <si>
-    <t xml:space="preserve">RNC 2026-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A proposta do medidor de espessura em linha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aprova o medidor em linha e cobra a homologação do segundo fornecedor de resina, ação da matriz de riscos.</t>
+    <t xml:space="preserve">RNC 2026-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A proposta dos dois medidores de espessura em linha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aprova os dois medidores em linha e cobra a homologação do segundo fornecedor de resina, ação da matriz de riscos.</t>
   </si>
   <si>
     <t xml:space="preserve">Ata da análise crítica de 18/02/2027</t>
@@ -1178,19 +1208,19 @@
     <t xml:space="preserve">A resina nova liberada para uso</t>
   </si>
   <si>
-    <t xml:space="preserve">Mudança registrada: resina do segundo fornecedor na extrusora 3, com lote piloto de duas bobinas, o lote 135.</t>
+    <t xml:space="preserve">Mudança registrada: resina do segundo fornecedor na extrusora 3, depois do lote piloto 127, de duas bobinas; o lote 135 é o primeiro da produção regular.</t>
   </si>
   <si>
     <t xml:space="preserve">Registro de mudança de 14/05/2027</t>
   </si>
   <si>
-    <t xml:space="preserve">O lote piloto, para liberar</t>
+    <t xml:space="preserve">O lote 135, para liberar</t>
   </si>
   <si>
     <t xml:space="preserve">Bobina 1 com 37,4 µm, segregada. Bobina 2 com 39,1 µm, liberada e embarcada em 17/05.</t>
   </si>
   <si>
-    <t xml:space="preserve">RNC 2027-19</t>
+    <t xml:space="preserve">Registro de produto não conforme 2027-19</t>
   </si>
   <si>
     <t xml:space="preserve">A bobina 2, no cliente A</t>
@@ -1199,7 +1229,7 @@
     <t xml:space="preserve">Cliente A reclama de filme fino no lote 135. Bobina recolhida e reposta em 26/05.</t>
   </si>
   <si>
-    <t xml:space="preserve">RNC 2027-22</t>
+    <t xml:space="preserve">Registro de produto não conforme 2027-22</t>
   </si>
   <si>
     <t xml:space="preserve">A dúvida sobre a medição</t>
@@ -1265,7 +1295,7 @@
     <t xml:space="preserve">7.1.6</t>
   </si>
   <si>
-    <t xml:space="preserve">Gerente de produção</t>
+    <t xml:space="preserve">Gerente industrial</t>
   </si>
   <si>
     <t xml:space="preserve">Gerente de RH</t>
@@ -1887,11 +1917,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="16709631"/>
-        <c:axId val="31603410"/>
+        <c:axId val="86139810"/>
+        <c:axId val="40389438"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="16709631"/>
+        <c:axId val="86139810"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1923,7 +1953,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31603410"/>
+        <c:crossAx val="40389438"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1931,7 +1961,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31603410"/>
+        <c:axId val="40389438"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1971,7 +2001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="16709631"/>
+        <c:crossAx val="86139810"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -3328,11 +3358,11 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Estudo da série em que o passo aconteceu" promptTitle="Opções" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="D8:D37" type="list">
-      <formula1>Estudos!$C$5:$C$33</formula1>
+      <formula1>Estudos!$C$5:$C$38</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Estudo que recebeu a saída deste passo" promptTitle="Opções" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="H8:H37" type="list">
-      <formula1>Estudos!$C$5:$C$33</formula1>
+      <formula1>Estudos!$C$5:$C$38</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -5911,7 +5941,7 @@
       <formula2>12</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" prompt="Estudo da série a que a atividade pertence" promptTitle="Opções" showDropDown="false" showErrorMessage="false" showInputMessage="true" sqref="D10:D49" type="list">
-      <formula1>Estudos!$C$5:$C$33</formula1>
+      <formula1>Estudos!$C$5:$C$38</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Mensal, bimestral, trimestral, semestral ou anual" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="G10:G49" type="list">
@@ -5936,7 +5966,7 @@
     <tabColor rgb="FF5B6B76"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:G33"/>
+  <dimension ref="B1:G38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -6017,16 +6047,16 @@
         <v>134</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E6" s="23" t="s">
         <v>131</v>
       </c>
       <c r="F6" s="23" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G6" s="23" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6034,10 +6064,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E7" s="23" t="s">
         <v>131</v>
@@ -6046,7 +6076,7 @@
         <v>132</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6054,16 +6084,16 @@
         <v>4</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>131</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G8" s="23" t="s">
         <v>141</v>
@@ -6103,10 +6133,10 @@
         <v>131</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6114,19 +6144,19 @@
         <v>7</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E11" s="23" t="s">
         <v>131</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6134,19 +6164,19 @@
         <v>8</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6154,19 +6184,19 @@
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F13" s="23" t="s">
         <v>132</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6174,19 +6204,19 @@
         <v>10</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="E14" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="D14" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>153</v>
-      </c>
       <c r="F14" s="23" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6194,13 +6224,13 @@
         <v>11</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>161</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F15" s="23" t="s">
         <v>162</v>
@@ -6217,16 +6247,16 @@
         <v>164</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6234,16 +6264,16 @@
         <v>13</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D17" s="23" t="s">
         <v>168</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="G17" s="23" t="s">
         <v>169</v>
@@ -6257,16 +6287,16 @@
         <v>170</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F18" s="23" t="s">
         <v>132</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6274,19 +6304,19 @@
         <v>15</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F19" s="23" t="s">
         <v>132</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6294,19 +6324,19 @@
         <v>16</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6314,16 +6344,16 @@
         <v>17</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D21" s="23" t="s">
         <v>177</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="G21" s="23" t="s">
         <v>178</v>
@@ -6337,16 +6367,16 @@
         <v>179</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6354,16 +6384,16 @@
         <v>19</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="G23" s="23" t="s">
         <v>183</v>
@@ -6377,13 +6407,13 @@
         <v>184</v>
       </c>
       <c r="D24" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="E24" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="E24" s="23" t="s">
-        <v>182</v>
-      </c>
       <c r="F24" s="23" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G24" s="23" t="s">
         <v>186</v>
@@ -6400,13 +6430,13 @@
         <v>188</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6414,19 +6444,19 @@
         <v>22</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6434,19 +6464,19 @@
         <v>23</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="G27" s="23" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6454,19 +6484,19 @@
         <v>24</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D28" s="23" t="s">
         <v>194</v>
       </c>
       <c r="E28" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" s="23" t="s">
         <v>195</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="G28" s="23" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6474,19 +6504,19 @@
         <v>25</v>
       </c>
       <c r="C29" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>196</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="G29" s="23" t="s">
         <v>197</v>
-      </c>
-      <c r="D29" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6494,16 +6524,16 @@
         <v>26</v>
       </c>
       <c r="C30" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D30" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="E30" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="E30" s="23" t="s">
-        <v>195</v>
-      </c>
       <c r="F30" s="23" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="G30" s="23" t="s">
         <v>201</v>
@@ -6517,16 +6547,16 @@
         <v>202</v>
       </c>
       <c r="D31" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="G31" s="23" t="s">
         <v>203</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6534,19 +6564,19 @@
         <v>28</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="G32" s="23" t="s">
         <v>205</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>140</v>
-      </c>
-      <c r="G32" s="23" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6554,19 +6584,119 @@
         <v>29</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>207</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F33" s="23" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="G33" s="23" t="s">
         <v>208</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="F34" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="G34" s="23" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="G35" s="23" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="F36" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="G36" s="23" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="G37" s="23" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="G38" s="23" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -6602,7 +6732,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -6611,7 +6741,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -6632,20 +6762,20 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="9" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="24" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="C6" s="24"/>
       <c r="D6" s="24"/>
@@ -6661,70 +6791,70 @@
         <v>0</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C8" s="13" t="n">
         <f aca="false">IF(COUNTA(Rastro!D8:D37)=0,0,SUMPRODUCT((Rastro!D8:D37&lt;&gt;"")/COUNTIF(Rastro!D8:D37,Rastro!D8:D37&amp;"")))</f>
         <v>0</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="C9" s="13" t="str">
         <f aca="false">IF(COUNT(Rastro!C8:C37)=0,"",MAX(Rastro!C8:C37)-MIN(Rastro!C8:C37))</f>
         <v/>
       </c>
       <c r="D9" s="25" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="E9" s="25"/>
       <c r="F9" s="25"/>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="C10" s="13" t="str">
         <f aca="false">IF(COUNT(Rastro!I8:I37)=0,"",MAX(Rastro!I8:I37))</f>
         <v/>
       </c>
       <c r="D10" s="25" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="E10" s="25"/>
       <c r="F10" s="25"/>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C11" s="13" t="n">
         <f aca="false">SUMPRODUCT((Rastro!J8:J37&lt;&gt;"")*(Rastro!J8:J37&lt;&gt;"OK"))</f>
         <v>0</v>
       </c>
       <c r="D11" s="25" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="24" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="C12" s="24"/>
       <c r="D12" s="24"/>
@@ -6733,14 +6863,14 @@
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="C13" s="13" t="str">
         <f aca="false">IF(Calendário!E5="","",Calendário!E5)</f>
         <v/>
       </c>
       <c r="D13" s="25" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="E13" s="25"/>
       <c r="F13" s="25"/>
@@ -6754,21 +6884,21 @@
         <v>0</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="E14" s="25"/>
       <c r="F14" s="25"/>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="C15" s="13" t="n">
         <f aca="false">SUM(Calendário!U10:U49)</f>
         <v>0</v>
       </c>
       <c r="D15" s="25" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="E15" s="25"/>
       <c r="F15" s="25"/>
@@ -6782,21 +6912,21 @@
         <v>0</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="E16" s="25"/>
       <c r="F16" s="25"/>
     </row>
     <row r="17" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="C17" s="26" t="str">
         <f aca="false">IFERROR(SUM(Calendário!V10:V49)/SUM(Calendário!U10:U49),"")</f>
         <v/>
       </c>
       <c r="D17" s="25" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="E17" s="25"/>
       <c r="F17" s="25"/>
@@ -6810,49 +6940,49 @@
         <v>0</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="E18" s="25"/>
       <c r="F18" s="25"/>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C19" s="13" t="n">
         <f aca="false">COUNTIF(Calendário!Y10:Y49,"Com atraso")</f>
         <v>0</v>
       </c>
       <c r="D19" s="25" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E19" s="25"/>
       <c r="F19" s="25"/>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="C20" s="13" t="n">
         <f aca="false">SUM(Calendário!X10:X49)</f>
         <v>0</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E20" s="25"/>
       <c r="F20" s="25"/>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C21" s="13" t="n">
         <f aca="false">SUMPRODUCT((Calendário!Z10:Z49&lt;&gt;"")*(Calendário!Z10:Z49&lt;&gt;"OK"))</f>
         <v>0</v>
       </c>
       <c r="D21" s="25" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="E21" s="25"/>
       <c r="F21" s="25"/>
@@ -6880,7 +7010,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="27" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6973,7 +7103,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -6981,7 +7111,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -6992,13 +7122,13 @@
         <v>94</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7006,7 +7136,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="5"/>
@@ -7016,7 +7146,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="5"/>
@@ -7026,7 +7156,7 @@
         <v>3</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="5"/>
@@ -7036,7 +7166,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="5"/>
@@ -7046,7 +7176,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="5"/>
@@ -7056,7 +7186,7 @@
         <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="5"/>
@@ -7066,7 +7196,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="5"/>
@@ -7076,7 +7206,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="5"/>
@@ -7086,7 +7216,7 @@
         <v>9</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="5"/>
@@ -7096,7 +7226,7 @@
         <v>10</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="5"/>
@@ -7106,7 +7236,7 @@
         <v>11</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="5"/>
@@ -7116,7 +7246,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="5"/>
@@ -7131,7 +7261,7 @@
     </row>
     <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="16" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="13" t="n">
@@ -7141,7 +7271,7 @@
     </row>
     <row r="20" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="16" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="C20" s="16"/>
       <c r="D20" s="13" t="n">
@@ -7151,7 +7281,7 @@
     </row>
     <row r="21" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="16" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="13" t="n">
@@ -7161,7 +7291,7 @@
     </row>
     <row r="22" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="16" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="C22" s="16"/>
       <c r="D22" s="13" t="n">
@@ -7171,7 +7301,7 @@
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="16" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="C23" s="16"/>
       <c r="D23" s="26" t="n">
@@ -7256,7 +7386,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -7285,7 +7415,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -7314,11 +7444,11 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="28" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="E4" s="28"/>
       <c r="F4" s="28"/>
@@ -7349,7 +7479,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="28" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="E5" s="28"/>
       <c r="F5" s="28"/>
@@ -7376,11 +7506,11 @@
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="28" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
@@ -7407,11 +7537,11 @@
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="28" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="E7" s="28"/>
       <c r="F7" s="28"/>
@@ -7438,7 +7568,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="29" t="n">
@@ -7450,7 +7580,7 @@
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="30" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
@@ -7518,19 +7648,19 @@
         <v>46188</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="H12" s="34" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="I12" s="13" t="str">
         <f aca="false">""</f>
@@ -7553,19 +7683,19 @@
         <v>46213</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="H13" s="34" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="I13" s="13" t="n">
         <f aca="false">IF(OR(C13="",C12=""),"",C13-C12)</f>
@@ -7580,7 +7710,7 @@
       <c r="M13" s="14"/>
       <c r="N13" s="14"/>
     </row>
-    <row r="14" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="11" t="n">
         <v>3</v>
       </c>
@@ -7588,19 +7718,19 @@
         <v>46220</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="I14" s="13" t="n">
         <f aca="false">IF(OR(C14="",C13=""),"",C14-C13)</f>
@@ -7615,7 +7745,7 @@
       <c r="M14" s="14"/>
       <c r="N14" s="14"/>
     </row>
-    <row r="15" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="11" t="n">
         <v>4</v>
       </c>
@@ -7623,19 +7753,19 @@
         <v>46227</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="I15" s="13" t="n">
         <f aca="false">IF(OR(C15="",C14=""),"",C15-C14)</f>
@@ -7658,19 +7788,19 @@
         <v>46271</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="I16" s="13" t="n">
         <f aca="false">IF(OR(C16="",C15=""),"",C16-C15)</f>
@@ -7693,19 +7823,19 @@
         <v>46294</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="I17" s="13" t="n">
         <f aca="false">IF(OR(C17="",C16=""),"",C17-C16)</f>
@@ -7728,19 +7858,19 @@
         <v>46301</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="I18" s="13" t="n">
         <f aca="false">IF(OR(C18="",C17=""),"",C18-C17)</f>
@@ -7763,19 +7893,19 @@
         <v>46370</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="H19" s="34" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="I19" s="13" t="n">
         <f aca="false">IF(OR(C19="",C18=""),"",C19-C18)</f>
@@ -7798,19 +7928,19 @@
         <v>46437</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E20" s="34" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I20" s="13" t="n">
         <f aca="false">IF(OR(C20="",C19=""),"",C20-C19)</f>
@@ -7833,19 +7963,19 @@
         <v>46493</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E21" s="34" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="F21" s="34" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="H21" s="34" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I21" s="13" t="n">
         <f aca="false">IF(OR(C21="",C20=""),"",C21-C20)</f>
@@ -7868,19 +7998,19 @@
         <v>46538</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="F22" s="34" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="I22" s="13" t="n">
         <f aca="false">IF(OR(C22="",C21=""),"",C22-C21)</f>
@@ -7903,13 +8033,13 @@
         <v>46552</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="F23" s="34" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="G23" s="34"/>
       <c r="H23" s="34"/>
@@ -7975,7 +8105,7 @@
         <v>98</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="I26" s="13" t="s">
         <v>100</v>
@@ -8023,7 +8153,7 @@
         <v>114</v>
       </c>
       <c r="X26" s="13" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="Y26" s="13" t="s">
         <v>115</v>
@@ -8078,38 +8208,38 @@
         <v>1</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="F28" s="34" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G28" s="36" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H28" s="37" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="L28" s="37"/>
       <c r="M28" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="N28" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="O28" s="37"/>
       <c r="P28" s="37"/>
@@ -8151,40 +8281,40 @@
         <v>2</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F29" s="34" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="G29" s="36" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H29" s="37" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="J29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="K29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="L29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="N29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="O29" s="37"/>
       <c r="P29" s="37"/>
@@ -8226,40 +8356,40 @@
         <v>3</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="D30" s="34" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="F30" s="34" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G30" s="36" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H30" s="37" t="n">
         <v>1</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="L30" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M30" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="N30" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="O30" s="37"/>
       <c r="P30" s="37"/>
@@ -8301,25 +8431,25 @@
         <v>4</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D31" s="34" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="F31" s="34" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H31" s="37" t="n">
         <v>1</v>
       </c>
       <c r="I31" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="J31" s="37"/>
       <c r="K31" s="37"/>
@@ -8366,19 +8496,19 @@
         <v>5</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="D32" s="34" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="F32" s="34" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G32" s="36" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H32" s="37" t="n">
         <v>5</v>
@@ -8388,10 +8518,10 @@
       <c r="K32" s="37"/>
       <c r="L32" s="37"/>
       <c r="M32" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="N32" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="O32" s="37"/>
       <c r="P32" s="37"/>
@@ -8433,31 +8563,31 @@
         <v>6</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="F33" s="34" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="G33" s="36" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H33" s="37" t="n">
         <v>2</v>
       </c>
       <c r="I33" s="37"/>
       <c r="J33" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="K33" s="37"/>
       <c r="L33" s="37"/>
       <c r="M33" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="N33" s="37"/>
       <c r="O33" s="37"/>
@@ -8500,31 +8630,31 @@
         <v>7</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="F34" s="34" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G34" s="36" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H34" s="37" t="n">
         <v>2</v>
       </c>
       <c r="I34" s="37"/>
       <c r="J34" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="K34" s="37"/>
       <c r="L34" s="37"/>
       <c r="M34" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="N34" s="37"/>
       <c r="O34" s="37"/>
@@ -8567,30 +8697,30 @@
         <v>8</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="D35" s="34" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="F35" s="34" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G35" s="36" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H35" s="37" t="n">
         <v>1</v>
       </c>
       <c r="I35" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="J35" s="37"/>
       <c r="K35" s="37"/>
       <c r="L35" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M35" s="37"/>
       <c r="N35" s="37"/>
@@ -8634,26 +8764,26 @@
         <v>9</v>
       </c>
       <c r="C36" s="33" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="D36" s="34" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="F36" s="34" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G36" s="36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H36" s="37" t="n">
         <v>2</v>
       </c>
       <c r="I36" s="37"/>
       <c r="J36" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="K36" s="37"/>
       <c r="L36" s="37"/>
@@ -8699,19 +8829,19 @@
         <v>10</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F37" s="34" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G37" s="36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H37" s="37" t="n">
         <v>4</v>
@@ -8720,7 +8850,7 @@
       <c r="J37" s="37"/>
       <c r="K37" s="37"/>
       <c r="L37" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M37" s="37"/>
       <c r="N37" s="37"/>
@@ -8764,19 +8894,19 @@
         <v>11</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D38" s="34" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="F38" s="34" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="G38" s="36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H38" s="37" t="n">
         <v>3</v>
@@ -8784,7 +8914,7 @@
       <c r="I38" s="37"/>
       <c r="J38" s="37"/>
       <c r="K38" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="L38" s="37"/>
       <c r="M38" s="37"/>
@@ -8829,25 +8959,25 @@
         <v>12</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="F39" s="34" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H39" s="37" t="n">
         <v>1</v>
       </c>
       <c r="I39" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="J39" s="37"/>
       <c r="K39" s="37"/>
@@ -8894,19 +9024,19 @@
         <v>13</v>
       </c>
       <c r="C40" s="33" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D40" s="34" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="F40" s="34" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="G40" s="36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H40" s="37" t="n">
         <v>6</v>
@@ -8917,7 +9047,7 @@
       <c r="L40" s="37"/>
       <c r="M40" s="37"/>
       <c r="N40" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="O40" s="37"/>
       <c r="P40" s="37"/>
@@ -8959,16 +9089,16 @@
         <v>14</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E41" s="36" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="F41" s="34" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="G41" s="36" t="s">
         <v>132</v>
@@ -9022,16 +9152,16 @@
         <v>15</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="D42" s="34" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E42" s="36" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="F42" s="34" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="G42" s="36" t="s">
         <v>132</v>
@@ -9207,7 +9337,7 @@
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="16" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
@@ -9360,7 +9490,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B1" s="1" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -9389,7 +9519,7 @@
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -9418,11 +9548,11 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C4" s="4"/>
       <c r="D4" s="28" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="E4" s="28"/>
       <c r="F4" s="28"/>
@@ -9453,7 +9583,7 @@
       </c>
       <c r="C5" s="4"/>
       <c r="D5" s="28" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="E5" s="28"/>
       <c r="F5" s="28"/>
@@ -9480,11 +9610,11 @@
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="28" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="E6" s="28"/>
       <c r="F6" s="28"/>
@@ -9511,11 +9641,11 @@
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="28" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="E7" s="28"/>
       <c r="F7" s="28"/>
@@ -9542,7 +9672,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="29" t="n">
@@ -9554,7 +9684,7 @@
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="30" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
@@ -9622,19 +9752,19 @@
         <v>46279</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="F12" s="34" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="H12" s="34" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="I12" s="13" t="str">
         <f aca="false">""</f>
@@ -9657,19 +9787,19 @@
         <v>46288</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="F13" s="34" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="H13" s="34" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="I13" s="13" t="n">
         <f aca="false">IF(OR(C13="",C12=""),"",C13-C12)</f>
@@ -9692,19 +9822,19 @@
         <v>46436</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="H14" s="34" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="I14" s="13" t="n">
         <f aca="false">IF(OR(C14="",C13=""),"",C14-C13)</f>
@@ -9727,19 +9857,19 @@
         <v>46475</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="F15" s="34" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="H15" s="34" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I15" s="13" t="n">
         <f aca="false">IF(OR(C15="",C14=""),"",C15-C14)</f>
@@ -9754,7 +9884,7 @@
       <c r="M15" s="14"/>
       <c r="N15" s="14"/>
     </row>
-    <row r="16" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="11" t="n">
         <v>5</v>
       </c>
@@ -9762,19 +9892,19 @@
         <v>46521</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="F16" s="34" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="H16" s="34" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="I16" s="13" t="n">
         <f aca="false">IF(OR(C16="",C15=""),"",C16-C15)</f>
@@ -9797,19 +9927,19 @@
         <v>46521</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="I17" s="13" t="n">
         <f aca="false">IF(OR(C17="",C16=""),"",C17-C16)</f>
@@ -9832,19 +9962,19 @@
         <v>46531</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="F18" s="34" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="H18" s="34" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="I18" s="13" t="n">
         <f aca="false">IF(OR(C18="",C17=""),"",C18-C17)</f>
@@ -9867,19 +9997,19 @@
         <v>46550</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="H19" s="34" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I19" s="13" t="n">
         <f aca="false">IF(OR(C19="",C18=""),"",C19-C18)</f>
@@ -9902,19 +10032,19 @@
         <v>46558</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E20" s="34" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I20" s="13" t="n">
         <f aca="false">IF(OR(C20="",C19=""),"",C20-C19)</f>
@@ -9937,19 +10067,19 @@
         <v>46599</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E21" s="34" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="F21" s="34" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="H21" s="34" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="I21" s="13" t="n">
         <f aca="false">IF(OR(C21="",C20=""),"",C21-C20)</f>
@@ -9972,19 +10102,19 @@
         <v>46618</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="F22" s="34" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="H22" s="34" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I22" s="13" t="n">
         <f aca="false">IF(OR(C22="",C21=""),"",C22-C21)</f>
@@ -10007,13 +10137,13 @@
         <v>46660</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="F23" s="34" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="G23" s="34"/>
       <c r="H23" s="34"/>
@@ -10079,7 +10209,7 @@
         <v>98</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="I26" s="13" t="s">
         <v>100</v>
@@ -10127,7 +10257,7 @@
         <v>114</v>
       </c>
       <c r="X26" s="13" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="Y26" s="13" t="s">
         <v>115</v>
@@ -10182,47 +10312,47 @@
         <v>1</v>
       </c>
       <c r="C28" s="33" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="D28" s="34" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="F28" s="34" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="G28" s="36" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H28" s="37" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="L28" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M28" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="N28" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="O28" s="37"/>
       <c r="P28" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="Q28" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="R28" s="37"/>
       <c r="S28" s="37"/>
@@ -10261,47 +10391,47 @@
         <v>2</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="F29" s="34" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="G29" s="36" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H29" s="37" t="n">
         <v>1</v>
       </c>
       <c r="I29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="J29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="K29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="L29" s="37"/>
       <c r="M29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="N29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="O29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="P29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="Q29" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="R29" s="37"/>
       <c r="S29" s="37"/>
@@ -10340,19 +10470,19 @@
         <v>3</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="D30" s="34" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="F30" s="34" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="G30" s="36" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H30" s="37" t="n">
         <v>3</v>
@@ -10360,17 +10490,17 @@
       <c r="I30" s="37"/>
       <c r="J30" s="37"/>
       <c r="K30" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="L30" s="37"/>
       <c r="M30" s="37"/>
       <c r="N30" s="37"/>
       <c r="O30" s="37"/>
       <c r="P30" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="Q30" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="37"/>
@@ -10409,19 +10539,19 @@
         <v>4</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="D31" s="34" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="F31" s="34" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="G31" s="36" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="H31" s="37" t="n">
         <v>6</v>
@@ -10432,14 +10562,14 @@
       <c r="L31" s="37"/>
       <c r="M31" s="37"/>
       <c r="N31" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="O31" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="P31" s="37"/>
       <c r="Q31" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="R31" s="37"/>
       <c r="S31" s="37"/>
@@ -10478,16 +10608,16 @@
         <v>5</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="D32" s="34" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="F32" s="34" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="G32" s="36" t="s">
         <v>132</v>
@@ -10504,7 +10634,7 @@
       <c r="O32" s="37"/>
       <c r="P32" s="37"/>
       <c r="Q32" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="R32" s="37"/>
       <c r="S32" s="37"/>
@@ -10543,35 +10673,35 @@
         <v>6</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="F33" s="34" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="G33" s="36" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H33" s="37" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="J33" s="37"/>
       <c r="K33" s="37"/>
       <c r="L33" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M33" s="37"/>
       <c r="N33" s="37"/>
       <c r="O33" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="P33" s="37"/>
       <c r="Q33" s="37"/>
@@ -10612,35 +10742,35 @@
         <v>7</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="D34" s="34" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="F34" s="34" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="G34" s="36" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="H34" s="37" t="n">
         <v>1</v>
       </c>
       <c r="I34" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="J34" s="37"/>
       <c r="K34" s="37"/>
       <c r="L34" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M34" s="37"/>
       <c r="N34" s="37"/>
       <c r="O34" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="P34" s="37"/>
       <c r="Q34" s="37"/>
@@ -10681,19 +10811,19 @@
         <v>8</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="D35" s="34" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="F35" s="34" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="G35" s="36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H35" s="37" t="n">
         <v>6</v>
@@ -10704,7 +10834,7 @@
       <c r="L35" s="37"/>
       <c r="M35" s="37"/>
       <c r="N35" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="O35" s="37"/>
       <c r="P35" s="37"/>
@@ -10746,19 +10876,19 @@
         <v>9</v>
       </c>
       <c r="C36" s="33" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="D36" s="34" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="F36" s="34" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="G36" s="36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H36" s="37" t="n">
         <v>4</v>
@@ -10767,7 +10897,7 @@
       <c r="J36" s="37"/>
       <c r="K36" s="37"/>
       <c r="L36" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M36" s="37"/>
       <c r="N36" s="37"/>
@@ -10811,19 +10941,19 @@
         <v>10</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="F37" s="34" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="G37" s="36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H37" s="37" t="n">
         <v>3</v>
@@ -10831,7 +10961,7 @@
       <c r="I37" s="37"/>
       <c r="J37" s="37"/>
       <c r="K37" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="L37" s="37"/>
       <c r="M37" s="37"/>
@@ -10839,7 +10969,7 @@
       <c r="O37" s="37"/>
       <c r="P37" s="37"/>
       <c r="Q37" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="R37" s="37"/>
       <c r="S37" s="37"/>
@@ -10878,26 +11008,26 @@
         <v>11</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D38" s="34" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="F38" s="34" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="G38" s="36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H38" s="37" t="n">
         <v>2</v>
       </c>
       <c r="I38" s="37"/>
       <c r="J38" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="K38" s="37"/>
       <c r="L38" s="37"/>
@@ -10905,7 +11035,7 @@
       <c r="N38" s="37"/>
       <c r="O38" s="37"/>
       <c r="P38" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="Q38" s="37"/>
       <c r="R38" s="37"/>
@@ -10945,25 +11075,25 @@
         <v>12</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="F39" s="34" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="G39" s="36" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="H39" s="37" t="n">
         <v>1</v>
       </c>
       <c r="I39" s="37" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="J39" s="37"/>
       <c r="K39" s="37"/>
@@ -11010,16 +11140,16 @@
         <v>13</v>
       </c>
       <c r="C40" s="33" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="D40" s="34" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="F40" s="34" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="G40" s="36" t="s">
         <v>132</v>
@@ -11195,7 +11325,7 @@
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="16" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>

--- a/Caso-Integrado/Caso-Integrado-modelo.xlsx
+++ b/Caso-Integrado/Caso-Integrado-modelo.xlsx
@@ -1917,11 +1917,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="86139810"/>
-        <c:axId val="40389438"/>
+        <c:axId val="46253506"/>
+        <c:axId val="31772177"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="86139810"/>
+        <c:axId val="46253506"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1953,7 +1953,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40389438"/>
+        <c:crossAx val="31772177"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1961,7 +1961,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="40389438"/>
+        <c:axId val="31772177"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2001,7 +2001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86139810"/>
+        <c:crossAx val="46253506"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>

--- a/Caso-Integrado/Caso-Integrado-modelo.xlsx
+++ b/Caso-Integrado/Caso-Integrado-modelo.xlsx
@@ -1917,11 +1917,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="46253506"/>
-        <c:axId val="31772177"/>
+        <c:axId val="67415669"/>
+        <c:axId val="39033530"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="46253506"/>
+        <c:axId val="67415669"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1953,7 +1953,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="31772177"/>
+        <c:crossAx val="39033530"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1961,7 +1961,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="31772177"/>
+        <c:axId val="39033530"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2001,7 +2001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="46253506"/>
+        <c:crossAx val="67415669"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>

--- a/Caso-Integrado/Caso-Integrado-modelo.xlsx
+++ b/Caso-Integrado/Caso-Integrado-modelo.xlsx
@@ -1262,7 +1262,7 @@
     <t xml:space="preserve">A disponibilidade abaixo da meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Entradas: o lote 135, o micrômetro reprovado e as quebras de julho. Decisões: antecipar o medidor em linha e planejar a passagem do conhecimento do operador sênior.</t>
+    <t xml:space="preserve">Entradas: o lote 135, o micrômetro reprovado e as quebras de julho. Decisões: concluir a instalação dos dois medidores em linha, atrasada desde junho, e planejar a passagem do conhecimento do operador sênior.</t>
   </si>
   <si>
     <t xml:space="preserve">Ata da análise crítica de 19/08/2027</t>
@@ -1917,11 +1917,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="0"/>
-        <c:axId val="67415669"/>
-        <c:axId val="39033530"/>
+        <c:axId val="64859511"/>
+        <c:axId val="98843482"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="67415669"/>
+        <c:axId val="64859511"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1953,7 +1953,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39033530"/>
+        <c:crossAx val="98843482"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1961,7 +1961,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39033530"/>
+        <c:axId val="98843482"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -2001,7 +2001,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67415669"/>
+        <c:crossAx val="64859511"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="1"/>
@@ -10094,7 +10094,7 @@
       <c r="M21" s="14"/>
       <c r="N21" s="14"/>
     </row>
-    <row r="22" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="66.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="11" t="n">
         <v>11</v>
       </c>
